--- a/Modules/CVMod8/CVMod8_BOM.xlsx
+++ b/Modules/CVMod8/CVMod8_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\_discontinued\CVMod8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD0BF44-1F8C-4353-A444-94F6B6D53E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2EA0BC-AA8C-4469-A1B4-D8C62A3B415F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -179,15 +179,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Jumper 2.54mm</t>
   </si>
   <si>
@@ -322,9 +316,6 @@
     <t>https://www.tme.eu/de/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
-  </si>
-  <si>
     <t>https://www.buerklin.com/en/p/quadrios/wirewound-resistors/22p046/73P0034/</t>
   </si>
   <si>
@@ -636,6 +627,15 @@
   </si>
   <si>
     <t>LED 3mm Dome Bicolor</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
   </si>
 </sst>
 </file>
@@ -1548,7 +1548,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1583,16 +1583,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>35</v>
@@ -1606,10 +1606,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1618,7 +1618,7 @@
         <v>35</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1629,16 +1629,16 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>35</v>
@@ -1655,16 +1655,16 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1675,19 +1675,19 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1698,19 +1698,19 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1724,16 +1724,16 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1753,10 +1753,10 @@
         <v>29</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1776,10 +1776,10 @@
         <v>18</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1793,10 +1793,10 @@
         <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>34</v>
@@ -1813,16 +1813,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1833,19 +1833,19 @@
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1853,13 +1853,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
@@ -1868,7 +1868,7 @@
         <v>33</v>
       </c>
       <c r="J15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1882,16 +1882,16 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1905,16 +1905,16 @@
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
         <v>21</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1934,10 +1934,10 @@
         <v>21</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="J18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1945,19 +1945,19 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J20" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1974,13 +1974,13 @@
         <v>47</v>
       </c>
       <c r="E22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="J22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1988,19 +1988,19 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
         <v>47</v>
       </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="J23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2020,7 +2020,7 @@
         <v>42</v>
       </c>
       <c r="J24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2040,7 +2040,7 @@
         <v>46</v>
       </c>
       <c r="J25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2048,24 +2048,24 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E26" t="s">
-        <v>52</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="J26" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2073,22 +2073,22 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F34" s="3"/>
     </row>
@@ -2097,16 +2097,16 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2127,20 +2127,20 @@
     <hyperlink ref="F24" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
     <hyperlink ref="C35" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
     <hyperlink ref="F20" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F22" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F23" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F25" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="F26" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F35" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="F16:F17" r:id="rId22" display="https://www.tme.eu/hr/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/" xr:uid="{5FADD932-BCFE-4359-9848-C49990507EC0}"/>
-    <hyperlink ref="F18" r:id="rId23" xr:uid="{602FB34B-4263-4C36-BC2D-81826C90FB25}"/>
-    <hyperlink ref="F6" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="F16" r:id="rId25" xr:uid="{8CF96FC1-8911-43F0-8C6C-CE8960E073E1}"/>
-    <hyperlink ref="F17" r:id="rId26" xr:uid="{6E51F05D-E250-4EB0-A858-436A016DA914}"/>
-    <hyperlink ref="F3" r:id="rId27" xr:uid="{939F8E45-723D-41B4-9BC5-8908979DF58A}"/>
-    <hyperlink ref="F5" r:id="rId28" xr:uid="{140B10F4-4A3C-40F1-972D-6084884C3764}"/>
-    <hyperlink ref="F10" r:id="rId29" xr:uid="{0BA54AA4-F571-4833-BDFE-FD39388723DF}"/>
-    <hyperlink ref="J4" r:id="rId30" xr:uid="{07F2DD50-1D67-4DA2-AAA9-DE7BA181557B}"/>
+    <hyperlink ref="F25" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="F26" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="F35" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="F16:F17" r:id="rId20" display="https://www.tme.eu/hr/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/" xr:uid="{5FADD932-BCFE-4359-9848-C49990507EC0}"/>
+    <hyperlink ref="F6" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="F16" r:id="rId22" xr:uid="{8CF96FC1-8911-43F0-8C6C-CE8960E073E1}"/>
+    <hyperlink ref="F17" r:id="rId23" xr:uid="{6E51F05D-E250-4EB0-A858-436A016DA914}"/>
+    <hyperlink ref="F3" r:id="rId24" xr:uid="{939F8E45-723D-41B4-9BC5-8908979DF58A}"/>
+    <hyperlink ref="F5" r:id="rId25" xr:uid="{140B10F4-4A3C-40F1-972D-6084884C3764}"/>
+    <hyperlink ref="F10" r:id="rId26" xr:uid="{0BA54AA4-F571-4833-BDFE-FD39388723DF}"/>
+    <hyperlink ref="J4" r:id="rId27" xr:uid="{07F2DD50-1D67-4DA2-AAA9-DE7BA181557B}"/>
+    <hyperlink ref="F18" r:id="rId28" xr:uid="{57C222F4-52E8-4AE1-AE27-71793248CBB1}"/>
+    <hyperlink ref="F22" r:id="rId29" xr:uid="{54FC818B-7259-4A85-8167-71A609FF4BF8}"/>
+    <hyperlink ref="F23" r:id="rId30" xr:uid="{BBEE79C2-8CC8-4781-9059-BFBF94857E3D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
